--- a/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:18</t>
+    <t xml:space="preserve">2026-09-10 01:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:32</t>
+    <t xml:space="preserve">2026-09-12 22:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:43</t>
+    <t xml:space="preserve">2026-09-24 00:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>167.74</v>
+        <v>182.46</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>153.09</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>130.92</v>
+        <v>141.71</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>91.71</v>
+        <v>97.24</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>83.11</v>
+        <v>89.66</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>82.33</v>
+        <v>89.38</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>78.65</v>
+        <v>84.25</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>65.86</v>
+        <v>71.01</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>49.62</v>
+        <v>53.72</v>
       </c>
     </row>
     <row r="11">
@@ -658,7 +658,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>40</v>
+        <v>41.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:12</t>
+    <t xml:space="preserve">2026-10-02 16:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:06</t>
+    <t xml:space="preserve">2026-10-04 10:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:44</t>
+    <t xml:space="preserve">2026-10-05 16:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
